--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,11 @@
       <c r="AB65" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC65" s="4" t="inlineStr"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -14776,7 +14780,11 @@
       <c r="AB138" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC138" s="4" t="inlineStr"/>
+      <c r="AC138" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -17624,7 +17632,11 @@
       <c r="AB166" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC166" s="4" t="inlineStr"/>
+      <c r="AC166" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -18440,7 +18452,11 @@
       <c r="AB174" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC174" s="4" t="inlineStr"/>
+      <c r="AC174" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -19357,7 +19373,11 @@
       <c r="AB183" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC183" s="4" t="inlineStr"/>
+      <c r="AC183" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -21199,7 +21219,11 @@
       <c r="AB201" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC201" s="4" t="inlineStr"/>
+      <c r="AC201" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q16" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2741,8 +2741,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2925,8 +2925,8 @@
       <c r="S22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
@@ -3400,13 +3400,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5084,8 +5084,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -7313,10 +7313,10 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
@@ -8646,7 +8646,7 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -9668,7 +9668,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13844,8 +13844,8 @@
       <c r="S129" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U129" s="9" t="n">
         <v>0</v>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15127,13 +15127,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15183,8 +15183,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -19449,7 +19449,7 @@
         <v>0</v>
       </c>
       <c r="S184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T184" s="10" t="n">
         <v>1</v>
@@ -19851,7 +19851,7 @@
         <v>0</v>
       </c>
       <c r="Q188" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R188" s="9" t="n">
         <v>0</v>
@@ -21618,7 +21618,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21651,7 +21651,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -21816,7 +21816,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -22410,7 +22410,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22476,7 +22476,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC203"/>
+  <dimension ref="A1:AC204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2314,13 +2314,13 @@
         <v>2</v>
       </c>
       <c r="R16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
         <v>2</v>
       </c>
       <c r="R18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="9" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="9" t="n">
         <v>0</v>
@@ -4751,7 +4751,7 @@
         <v>2</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="9" t="n">
         <v>0</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5259,8 +5259,8 @@
       <c r="P45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>1</v>
+      <c r="Q45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>0</v>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7223,11 +7223,11 @@
       <c r="S64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="9" t="n">
-        <v>0</v>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V64" s="9" t="n">
         <v>0</v>
@@ -7313,7 +7313,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>1</v>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8675,8 +8675,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11404,8 +11404,8 @@
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
@@ -11910,10 +11910,10 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12953,8 +12953,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="S133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T133" s="9" t="n">
         <v>0</v>
@@ -15925,7 +15925,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15977,8 +15977,8 @@
       <c r="S150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T150" s="9" t="n">
-        <v>0</v>
+      <c r="T150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U150" s="9" t="n">
         <v>0</v>
@@ -16640,7 +16640,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16692,8 +16692,8 @@
       <c r="S157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T157" s="9" t="n">
-        <v>0</v>
+      <c r="T157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U157" s="9" t="n">
         <v>0</v>
@@ -16710,8 +16710,8 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -16741,7 +16741,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16811,8 +16811,8 @@
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
@@ -17250,7 +17250,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17320,8 +17320,8 @@
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -17444,11 +17444,11 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>7725085</v>
+        <v>28680567</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>One Astellas Toastmasters</t>
+          <t>KPMG Japan Toastmasters</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
@@ -17466,17 +17466,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L165" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M165" s="8" t="n">
@@ -17511,7 +17511,7 @@
         <v>0</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
@@ -17523,14 +17523,12 @@
         <v>0</v>
       </c>
       <c r="Z165" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB165" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="AB165" s="4" t="n"/>
       <c r="AC165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
@@ -17545,15 +17543,15 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>1592494</v>
+        <v>7725085</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Otemachi Toastmasters Club</t>
+          <t>One Astellas Toastmasters</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17567,17 +17565,17 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L166" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M166" s="8" t="n">
@@ -17594,16 +17592,16 @@
         </is>
       </c>
       <c r="P166" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q166" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R166" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S166" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T166" s="9" t="n">
         <v>0</v>
@@ -17611,8 +17609,8 @@
       <c r="U166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V166" s="10" t="n">
-        <v>4</v>
+      <c r="V166" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -17630,13 +17628,9 @@
         <v>1</v>
       </c>
       <c r="AB166" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC166" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -17650,15 +17644,15 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>4702</v>
+        <v>1592494</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Phoenix Club</t>
+          <t>Otemachi Toastmasters Club</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17672,17 +17666,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
@@ -17699,7 +17693,7 @@
         </is>
       </c>
       <c r="P167" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>1</v>
@@ -17708,7 +17702,7 @@
         <v>0</v>
       </c>
       <c r="S167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T167" s="9" t="n">
         <v>0</v>
@@ -17716,8 +17710,8 @@
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>0</v>
+      <c r="V167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
         <v>0</v>
@@ -17735,31 +17729,35 @@
         <v>1</v>
       </c>
       <c r="AB167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC167" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC167" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>1460128</v>
+        <v>4702</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Akihabara Toastmasters Club</t>
+          <t>Tokyo Phoenix Club</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17773,13 +17771,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17800,11 +17798,11 @@
         </is>
       </c>
       <c r="P168" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q168" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="Q168" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="R168" s="9" t="n">
         <v>0</v>
       </c>
@@ -17818,7 +17816,7 @@
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -17836,7 +17834,7 @@
         <v>1</v>
       </c>
       <c r="AB168" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC168" s="4" t="inlineStr"/>
     </row>
@@ -17852,15 +17850,15 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>1080113</v>
+        <v>1460128</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Chiyoda Toastmasters Club</t>
+          <t>Akihabara Toastmasters Club</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -17874,17 +17872,17 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K169" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L169" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L169" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M169" s="8" t="n">
@@ -17901,49 +17899,45 @@
         </is>
       </c>
       <c r="P169" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q169" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q169" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S169" s="10" t="n">
+      <c r="S169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA169" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB169" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T169" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V169" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z169" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA169" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB169" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC169" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -17957,15 +17951,15 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>7064510</v>
+        <v>1080113</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>MetLife Japan Toastmasters Club</t>
+          <t>Chiyoda Toastmasters Club</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -17979,13 +17973,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -18014,17 +18008,17 @@
       <c r="R170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S170" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T170" s="9" t="n">
-        <v>0</v>
+      <c r="S170" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T170" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U170" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V170" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W170" s="9" t="n">
         <v>0</v>
@@ -18042,11 +18036,11 @@
         <v>1</v>
       </c>
       <c r="AB170" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC170" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -18062,11 +18056,11 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>7640872</v>
+        <v>7064510</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Mizuho Toastmasters Club</t>
+          <t>MetLife Japan Toastmasters Club</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
@@ -18084,17 +18078,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K171" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L171" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M171" s="8" t="n">
@@ -18111,7 +18105,7 @@
         </is>
       </c>
       <c r="P171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q171" s="9" t="n">
         <v>0</v>
@@ -18147,9 +18141,13 @@
         <v>1</v>
       </c>
       <c r="AB171" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC171" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC171" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -18163,15 +18161,15 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>3797038</v>
+        <v>7640872</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Oval Toastmasters</t>
+          <t>Mizuho Toastmasters Club</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18212,7 +18210,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>0</v>
@@ -18223,8 +18221,8 @@
       <c r="S172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T172" s="10" t="n">
-        <v>1</v>
+      <c r="T172" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U172" s="9" t="n">
         <v>0</v>
@@ -18248,7 +18246,7 @@
         <v>1</v>
       </c>
       <c r="AB172" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC172" s="4" t="inlineStr"/>
     </row>
@@ -18264,15 +18262,15 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>1994020</v>
+        <v>3797038</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Tokyo ESS Toastmasters Club</t>
+          <t>Oval Toastmasters</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18286,10 +18284,10 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K173" s="4" t="n">
         <v>0</v>
@@ -18313,7 +18311,7 @@
         </is>
       </c>
       <c r="P173" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q173" s="9" t="n">
         <v>0</v>
@@ -18342,14 +18340,14 @@
       <c r="Y173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z173" s="9" t="n">
-        <v>0</v>
+      <c r="Z173" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA173" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC173" s="4" t="inlineStr"/>
     </row>
@@ -18361,19 +18359,19 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>2932428</v>
+        <v>1994020</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Big Tree Toastmasters Club</t>
+          <t>Tokyo ESS Toastmasters Club</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18387,17 +18385,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L174" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M174" s="8" t="n">
@@ -18423,7 +18421,7 @@
         <v>0</v>
       </c>
       <c r="S174" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T174" s="10" t="n">
         <v>1</v>
@@ -18432,7 +18430,7 @@
         <v>0</v>
       </c>
       <c r="V174" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W174" s="9" t="n">
         <v>0</v>
@@ -18443,20 +18441,16 @@
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="10" t="n">
-        <v>1</v>
+      <c r="Z174" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC174" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -18470,15 +18464,15 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>2805262</v>
+        <v>2932428</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Hajime no Ippo Club</t>
+          <t>Big Tree Toastmasters Club</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18492,17 +18486,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L175" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M175" s="8" t="n">
@@ -18522,22 +18516,22 @@
         <v>0</v>
       </c>
       <c r="Q175" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R175" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V175" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
@@ -18555,11 +18549,11 @@
         <v>1</v>
       </c>
       <c r="AB175" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC175" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -18575,11 +18569,11 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>1544579</v>
+        <v>2805262</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Meguro Toastmasters Club</t>
+          <t>Hajime no Ippo Club</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
@@ -18597,10 +18591,10 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K176" s="4" t="n">
         <v>0</v>
@@ -18627,7 +18621,7 @@
         <v>0</v>
       </c>
       <c r="Q176" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R176" s="9" t="n">
         <v>0</v>
@@ -18660,9 +18654,13 @@
         <v>1</v>
       </c>
       <c r="AB176" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC176" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC176" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -18676,15 +18674,15 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>1293910</v>
+        <v>1544579</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Sakurazaka</t>
+          <t>Meguro Toastmasters Club</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18698,13 +18696,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18734,16 +18732,16 @@
         <v>0</v>
       </c>
       <c r="S177" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T177" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T177" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U177" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -18761,7 +18759,7 @@
         <v>1</v>
       </c>
       <c r="AB177" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC177" s="4" t="inlineStr"/>
     </row>
@@ -18777,15 +18775,15 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>7221012</v>
+        <v>1293910</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Shimazuyama</t>
+          <t>Sakurazaka</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18799,13 +18797,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -18835,16 +18833,16 @@
         <v>0</v>
       </c>
       <c r="S178" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V178" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
@@ -18862,7 +18860,7 @@
         <v>1</v>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC178" s="4" t="inlineStr"/>
     </row>
@@ -18878,15 +18876,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>2320</v>
+        <v>7221012</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Bay Toastmasters</t>
+          <t>Shimazuyama</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18900,13 +18898,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -18927,7 +18925,7 @@
         </is>
       </c>
       <c r="P179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q179" s="9" t="n">
         <v>0</v>
@@ -18945,7 +18943,7 @@
         <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
@@ -18956,14 +18954,14 @@
       <c r="Y179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z179" s="9" t="n">
-        <v>0</v>
+      <c r="Z179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA179" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB179" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC179" s="4" t="inlineStr"/>
     </row>
@@ -18975,15 +18973,15 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>4947</v>
+        <v>2320</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Breakfast Toastmasters Club</t>
+          <t>Tokyo Bay Toastmasters</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
@@ -19001,17 +18999,17 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L180" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M180" s="8" t="n">
@@ -19028,7 +19026,7 @@
         </is>
       </c>
       <c r="P180" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q180" s="9" t="n">
         <v>0</v>
@@ -19046,7 +19044,7 @@
         <v>0</v>
       </c>
       <c r="V180" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W180" s="9" t="n">
         <v>0</v>
@@ -19064,13 +19062,9 @@
         <v>1</v>
       </c>
       <c r="AB180" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC180" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -19084,11 +19078,11 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>5633576</v>
+        <v>4947</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Business Lunch Toastmasters</t>
+          <t>Breakfast Toastmasters Club</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
@@ -19106,17 +19100,17 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M181" s="8" t="n">
@@ -19133,25 +19127,25 @@
         </is>
       </c>
       <c r="P181" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q181" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R181" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S181" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T181" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T181" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U181" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W181" s="9" t="n">
         <v>0</v>
@@ -19162,16 +19156,20 @@
       <c r="Y181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z181" s="9" t="n">
-        <v>0</v>
+      <c r="Z181" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA181" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB181" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC181" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC181" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -19185,15 +19183,15 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>1276907</v>
+        <v>5633576</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Nihonbashi Century Toastmasters Club</t>
+          <t>Business Lunch Toastmasters</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -19207,17 +19205,17 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L182" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M182" s="8" t="n">
@@ -19234,10 +19232,10 @@
         </is>
       </c>
       <c r="P182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" s="9" t="n">
         <v>0</v>
@@ -19248,11 +19246,11 @@
       <c r="T182" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U182" s="10" t="n">
-        <v>1</v>
+      <c r="U182" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V182" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
@@ -19263,14 +19261,14 @@
       <c r="Y182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z182" s="10" t="n">
-        <v>1</v>
+      <c r="Z182" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA182" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB182" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC182" s="4" t="inlineStr"/>
     </row>
@@ -19286,15 +19284,15 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>1167588</v>
+        <v>1276907</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Shimbashi Toastmasters Club</t>
+          <t>Nihonbashi Century Toastmasters Club</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -19308,10 +19306,10 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K183" s="4" t="n">
         <v>2</v>
@@ -19335,7 +19333,7 @@
         </is>
       </c>
       <c r="P183" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q183" s="9" t="n">
         <v>0</v>
@@ -19346,11 +19344,11 @@
       <c r="S183" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T183" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U183" s="9" t="n">
-        <v>0</v>
+      <c r="T183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U183" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V183" s="9" t="n">
         <v>2</v>
@@ -19371,13 +19369,9 @@
         <v>1</v>
       </c>
       <c r="AB183" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC183" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -19391,35 +19385,35 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>1674</v>
+        <v>1167588</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Toastmasters Club</t>
+          <t>Shimbashi Toastmasters Club</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G184" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J184" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K184" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F184" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G184" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H184" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I184" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="J184" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="K184" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
@@ -19440,7 +19434,7 @@
         </is>
       </c>
       <c r="P184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q184" s="9" t="n">
         <v>0</v>
@@ -19451,14 +19445,14 @@
       <c r="S184" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T184" s="10" t="n">
-        <v>1</v>
+      <c r="T184" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U184" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V184" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W184" s="9" t="n">
         <v>0</v>
@@ -19476,11 +19470,11 @@
         <v>1</v>
       </c>
       <c r="AB184" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC184" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -19496,15 +19490,15 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>3996016</v>
+        <v>1674</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>UTAGE Toastmasters Club</t>
+          <t>Tokyo Toastmasters Club</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -19518,17 +19512,17 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L185" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L185" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M185" s="8" t="n">
@@ -19554,16 +19548,16 @@
         <v>0</v>
       </c>
       <c r="S185" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U185" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V185" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W185" s="9" t="n">
         <v>0</v>
@@ -19581,9 +19575,13 @@
         <v>1</v>
       </c>
       <c r="AB185" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC185" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC185" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -19593,39 +19591,39 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>1362687</v>
+        <v>3996016</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>FCCJ Toastmasters Club</t>
+          <t>UTAGE Toastmasters Club</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G186" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J186" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K186" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F186" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G186" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H186" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J186" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K186" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -19648,24 +19646,24 @@
       <c r="P186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" s="10" t="n">
+      <c r="Q186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V186" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R186" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T186" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U186" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V186" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W186" s="9" t="n">
         <v>0</v>
       </c>
@@ -19682,7 +19680,7 @@
         <v>1</v>
       </c>
       <c r="AB186" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC186" s="4" t="inlineStr"/>
     </row>
@@ -19698,15 +19696,15 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>28677087</v>
+        <v>1362687</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>LSEG Japan Toastmasters Club</t>
+          <t>FCCJ Toastmasters Club</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19720,13 +19718,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
@@ -19749,8 +19747,8 @@
       <c r="P187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" s="9" t="n">
-        <v>0</v>
+      <c r="Q187" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R187" s="9" t="n">
         <v>0</v>
@@ -19765,7 +19763,7 @@
         <v>0</v>
       </c>
       <c r="V187" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W187" s="9" t="n">
         <v>0</v>
@@ -19783,7 +19781,7 @@
         <v>1</v>
       </c>
       <c r="AB187" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC187" s="4" t="inlineStr"/>
     </row>
@@ -19799,11 +19797,11 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>2918401</v>
+        <v>28677087</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>New Bridge Toastmasters Club</t>
+          <t>LSEG Japan Toastmasters Club</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
@@ -19821,17 +19819,17 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L188" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L188" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M188" s="8" t="n">
@@ -19851,7 +19849,7 @@
         <v>0</v>
       </c>
       <c r="Q188" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R188" s="9" t="n">
         <v>0</v>
@@ -19866,7 +19864,7 @@
         <v>0</v>
       </c>
       <c r="V188" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W188" s="9" t="n">
         <v>0</v>
@@ -19900,11 +19898,11 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>1034062</v>
+        <v>2918401</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Shibuya Toastmasters Club</t>
+          <t>New Bridge Toastmasters Club</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
@@ -19922,17 +19920,17 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L189" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M189" s="8" t="n">
@@ -19952,7 +19950,7 @@
         <v>0</v>
       </c>
       <c r="Q189" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R189" s="9" t="n">
         <v>0</v>
@@ -19967,7 +19965,7 @@
         <v>0</v>
       </c>
       <c r="V189" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W189" s="9" t="n">
         <v>0</v>
@@ -19985,7 +19983,7 @@
         <v>1</v>
       </c>
       <c r="AB189" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC189" s="4" t="inlineStr"/>
     </row>
@@ -20001,15 +19999,15 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>1039199</v>
+        <v>1034062</v>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Tokyo International Toastmasters Club</t>
+          <t>Shibuya Toastmasters Club</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>10</v>
@@ -20023,17 +20021,17 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L190" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L190" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M190" s="8" t="n">
@@ -20050,7 +20048,7 @@
         </is>
       </c>
       <c r="P190" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q190" s="9" t="n">
         <v>0</v>
@@ -20061,14 +20059,14 @@
       <c r="S190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T190" s="10" t="n">
-        <v>1</v>
+      <c r="T190" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U190" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V190" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W190" s="9" t="n">
         <v>0</v>
@@ -20086,13 +20084,9 @@
         <v>1</v>
       </c>
       <c r="AB190" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC190" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -20106,15 +20100,15 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>4674</v>
+        <v>1039199</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Yamanote Toastmasters Club</t>
+          <t>Tokyo International Toastmasters Club</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -20128,17 +20122,17 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J191" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M191" s="8" t="n">
@@ -20155,10 +20149,10 @@
         </is>
       </c>
       <c r="P191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q191" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R191" s="9" t="n">
         <v>0</v>
@@ -20166,14 +20160,14 @@
       <c r="S191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T191" s="9" t="n">
-        <v>0</v>
+      <c r="T191" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U191" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
@@ -20191,9 +20185,13 @@
         <v>1</v>
       </c>
       <c r="AB191" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC191" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC191" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -20203,15 +20201,15 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>7323653</v>
+        <v>4674</v>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>CHIZAI Toastmasters Club</t>
+          <t>Yamanote Toastmasters Club</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
@@ -20229,10 +20227,10 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J192" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K192" s="4" t="n">
         <v>0</v>
@@ -20259,7 +20257,7 @@
         <v>0</v>
       </c>
       <c r="Q192" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R192" s="9" t="n">
         <v>0</v>
@@ -20292,7 +20290,7 @@
         <v>1</v>
       </c>
       <c r="AB192" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC192" s="4" t="inlineStr"/>
     </row>
@@ -20308,11 +20306,11 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>8643</v>
+        <v>7323653</v>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>KeyForce Club</t>
+          <t>CHIZAI Toastmasters Club</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
@@ -20330,10 +20328,10 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J193" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K193" s="4" t="n">
         <v>0</v>
@@ -20357,10 +20355,10 @@
         </is>
       </c>
       <c r="P193" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q193" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R193" s="9" t="n">
         <v>0</v>
@@ -20393,7 +20391,7 @@
         <v>1</v>
       </c>
       <c r="AB193" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC193" s="4" t="inlineStr"/>
     </row>
@@ -20409,15 +20407,15 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>8827</v>
+        <v>8643</v>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Omotesando Toastmasters Club</t>
+          <t>KeyForce Club</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20431,13 +20429,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J194" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -20469,14 +20467,14 @@
       <c r="S194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T194" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U194" s="10" t="n">
-        <v>1</v>
+      <c r="T194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V194" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W194" s="9" t="n">
         <v>0</v>
@@ -20494,13 +20492,9 @@
         <v>1</v>
       </c>
       <c r="AB194" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC194" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -20514,15 +20508,15 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>7898244</v>
+        <v>8827</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>SuMiTRUST University Toastmasters Club</t>
+          <t>Omotesando Toastmasters Club</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>10</v>
@@ -20536,13 +20530,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J195" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
@@ -20563,7 +20557,7 @@
         </is>
       </c>
       <c r="P195" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q195" s="9" t="n">
         <v>0</v>
@@ -20574,14 +20568,14 @@
       <c r="S195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U195" s="9" t="n">
-        <v>0</v>
+      <c r="T195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U195" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V195" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W195" s="9" t="n">
         <v>0</v>
@@ -20592,16 +20586,20 @@
       <c r="Y195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z195" s="9" t="n">
-        <v>0</v>
+      <c r="Z195" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA195" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB195" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC195" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC195" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -20615,15 +20613,15 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>3050495</v>
+        <v>7898244</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Tokyo American Club (TAC) Toastmasters</t>
+          <t>SuMiTRUST University Toastmasters Club</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>10</v>
@@ -20637,17 +20635,17 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L196" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L196" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M196" s="8" t="n">
@@ -20664,7 +20662,7 @@
         </is>
       </c>
       <c r="P196" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q196" s="9" t="n">
         <v>0</v>
@@ -20682,7 +20680,7 @@
         <v>0</v>
       </c>
       <c r="V196" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W196" s="9" t="n">
         <v>0</v>
@@ -20693,14 +20691,14 @@
       <c r="Y196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z196" s="10" t="n">
-        <v>1</v>
+      <c r="Z196" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA196" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB196" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC196" s="4" t="inlineStr"/>
     </row>
@@ -20716,11 +20714,11 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>817349</v>
+        <v>3050495</v>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Debate Toastmasters Club</t>
+          <t>Tokyo American Club (TAC) Toastmasters</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
@@ -20738,17 +20736,17 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J197" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L197" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L197" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M197" s="8" t="n">
@@ -20765,10 +20763,10 @@
         </is>
       </c>
       <c r="P197" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q197" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R197" s="9" t="n">
         <v>0</v>
@@ -20783,7 +20781,7 @@
         <v>0</v>
       </c>
       <c r="V197" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W197" s="9" t="n">
         <v>0</v>
@@ -20801,13 +20799,9 @@
         <v>1</v>
       </c>
       <c r="AB197" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC197" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -20817,15 +20811,15 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>5272656</v>
+        <v>817349</v>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>FORWARD Toastmasters Club</t>
+          <t>Tokyo Debate Toastmasters Club</t>
         </is>
       </c>
       <c r="E198" s="5" t="n">
@@ -20843,13 +20837,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J198" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -20870,10 +20864,10 @@
         </is>
       </c>
       <c r="P198" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q198" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R198" s="9" t="n">
         <v>0</v>
@@ -20888,7 +20882,7 @@
         <v>0</v>
       </c>
       <c r="V198" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W198" s="9" t="n">
         <v>0</v>
@@ -20906,9 +20900,13 @@
         <v>1</v>
       </c>
       <c r="AB198" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC198" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC198" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -20922,11 +20920,11 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>645544</v>
+        <v>5272656</v>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Minami Aoyama Business Toastmasters Club</t>
+          <t>FORWARD Toastmasters Club</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">
@@ -20947,10 +20945,10 @@
         <v>14</v>
       </c>
       <c r="J199" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -20989,7 +20987,7 @@
         <v>0</v>
       </c>
       <c r="V199" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W199" s="9" t="n">
         <v>0</v>
@@ -21007,13 +21005,9 @@
         <v>1</v>
       </c>
       <c r="AB199" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC199" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -21027,11 +21021,11 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>1299676</v>
+        <v>645544</v>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Omotesando Bilingual Toastmasters Club</t>
+          <t>Minami Aoyama Business Toastmasters Club</t>
         </is>
       </c>
       <c r="E200" s="5" t="n">
@@ -21049,17 +21043,17 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J200" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L200" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M200" s="8" t="n">
@@ -21079,7 +21073,7 @@
         <v>0</v>
       </c>
       <c r="Q200" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R200" s="9" t="n">
         <v>0</v>
@@ -21094,7 +21088,7 @@
         <v>0</v>
       </c>
       <c r="V200" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W200" s="9" t="n">
         <v>0</v>
@@ -21112,7 +21106,7 @@
         <v>1</v>
       </c>
       <c r="AB200" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC200" s="4" t="inlineStr">
         <is>
@@ -21132,11 +21126,11 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>1076364</v>
+        <v>1299676</v>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Pioneer Toastmasters Club</t>
+          <t>Omotesando Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
@@ -21157,10 +21151,10 @@
         <v>27</v>
       </c>
       <c r="J201" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21184,13 +21178,13 @@
         <v>0</v>
       </c>
       <c r="Q201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R201" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S201" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T201" s="9" t="n">
         <v>0</v>
@@ -21199,7 +21193,7 @@
         <v>0</v>
       </c>
       <c r="V201" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W201" s="9" t="n">
         <v>0</v>
@@ -21217,11 +21211,11 @@
         <v>1</v>
       </c>
       <c r="AB201" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC201" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -21237,35 +21231,35 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>9430</v>
+        <v>1076364</v>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Bilingual</t>
+          <t>Pioneer Toastmasters Club</t>
         </is>
       </c>
       <c r="E202" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G202" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J202" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K202" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F202" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G202" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H202" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I202" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J202" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K202" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
@@ -21295,7 +21289,7 @@
         <v>0</v>
       </c>
       <c r="S202" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T202" s="9" t="n">
         <v>0</v>
@@ -21303,11 +21297,11 @@
       <c r="U202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V202" s="10" t="n">
-        <v>4</v>
+      <c r="V202" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W202" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X202" s="9" t="n">
         <v>0</v>
@@ -21322,9 +21316,13 @@
         <v>1</v>
       </c>
       <c r="AB202" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC202" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC202" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -21338,15 +21336,15 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>5032715</v>
+        <v>9430</v>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Midtown Toastmasters Club</t>
+          <t>Tokyo Bilingual</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F203" s="6" t="n">
         <v>10</v>
@@ -21360,13 +21358,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J203" s="4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
@@ -21404,35 +21402,136 @@
       <c r="U203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V203" s="9" t="n">
+      <c r="V203" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W203" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X203" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y203" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB203" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC203" s="4" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="n">
+        <v>5032715</v>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>Tokyo Midtown Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G204" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J204" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K204" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W203" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X203" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y203" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z203" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA203" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB203" s="4" t="n">
+      <c r="L204" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M204" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N204" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O204" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V204" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z204" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA204" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB204" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC203" s="4" t="inlineStr">
+      <c r="AC204" s="4" t="inlineStr">
         <is>
           <t>Select Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC203"/>
+  <autoFilter ref="A1:AC204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21618,7 +21717,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21816,13 +21915,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -21948,7 +22047,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -22047,7 +22146,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -22245,7 +22344,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -22344,7 +22443,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -22542,7 +22641,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22575,7 +22674,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -22608,7 +22707,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -22638,25 +22737,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -22707,7 +22806,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1196,8 +1196,8 @@
       <c r="S5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="9" t="n">
-        <v>0</v>
+      <c r="T5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U5" s="9" t="n">
         <v>0</v>
@@ -1259,17 +1259,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="10" t="n">
         <v>1</v>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2685,13 +2685,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3194,13 +3194,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3400,17 +3400,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3602,13 +3602,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3637,8 +3637,8 @@
       <c r="R29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="9" t="n">
-        <v>1</v>
+      <c r="S29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T29" s="9" t="n">
         <v>0</v>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3804,13 +3804,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" s="9" t="n">
         <v>0</v>
@@ -3905,17 +3905,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -4010,13 +4010,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4447,8 +4447,8 @@
       <c r="P37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" s="9" t="n">
-        <v>1</v>
+      <c r="Q37" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4923,17 +4923,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -4953,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -5028,13 +5028,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5129,13 +5129,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5230,13 +5230,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5335,13 +5335,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5440,13 +5440,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5545,17 +5545,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5650,13 +5650,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5688,8 +5688,8 @@
       <c r="S49" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T49" s="9" t="n">
-        <v>0</v>
+      <c r="T49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U49" s="9" t="n">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5953,13 +5953,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6058,13 +6058,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="9" t="n">
         <v>0</v>
@@ -6204,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6264,13 +6264,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6365,17 +6365,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6466,13 +6466,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6571,13 +6571,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6676,13 +6676,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6979,17 +6979,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7084,13 +7084,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7185,13 +7185,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7286,13 +7286,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7328,13 +7328,13 @@
         <v>1</v>
       </c>
       <c r="U65" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V65" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X65" s="9" t="n">
         <v>0</v>
@@ -7391,13 +7391,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7492,13 +7492,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7694,13 +7694,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7896,13 +7896,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7997,13 +7997,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8102,13 +8102,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8203,13 +8203,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8308,13 +8308,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8413,13 +8413,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8514,13 +8514,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8558,8 +8558,8 @@
       <c r="U77" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>3</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8619,13 +8619,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8720,13 +8720,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8821,13 +8821,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9027,13 +9027,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9128,13 +9128,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9229,13 +9229,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -9334,13 +9334,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9439,13 +9439,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9742,13 +9742,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9843,13 +9843,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10090,7 +10090,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10247,13 +10247,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10554,13 +10554,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>1</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10857,13 +10857,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10958,17 +10958,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11003,7 +11003,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11063,13 +11063,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11092,8 +11092,8 @@
       <c r="P102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" s="9" t="n">
-        <v>1</v>
+      <c r="Q102" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R102" s="9" t="n">
         <v>0</v>
@@ -11150,7 +11150,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11164,13 +11164,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11202,8 +11202,8 @@
       <c r="S103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T103" s="9" t="n">
-        <v>0</v>
+      <c r="T103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
@@ -11265,13 +11265,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11366,17 +11366,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11471,17 +11471,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11673,13 +11673,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11778,13 +11778,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11984,13 +11984,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12085,13 +12085,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12186,13 +12186,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12287,13 +12287,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12388,13 +12388,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12489,13 +12489,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12590,17 +12590,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12691,17 +12691,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12736,7 +12736,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12796,17 +12796,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12823,7 +12823,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -12998,13 +12998,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13099,13 +13099,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13200,13 +13200,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13301,13 +13301,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13402,13 +13402,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>0</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" s="10" t="n">
         <v>1</v>
@@ -13649,7 +13649,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13841,8 +13841,8 @@
       <c r="R129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S129" s="9" t="n">
-        <v>1</v>
+      <c r="S129" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T129" s="10" t="n">
         <v>1</v>
@@ -13907,13 +13907,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -14008,13 +14008,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14109,13 +14109,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14245,8 +14245,8 @@
       <c r="R133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S133" s="9" t="n">
-        <v>1</v>
+      <c r="S133" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T133" s="9" t="n">
         <v>0</v>
@@ -14311,13 +14311,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14412,13 +14412,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14614,13 +14614,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14715,13 +14715,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14921,13 +14921,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15066,8 +15066,8 @@
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="9" t="n">
-        <v>2</v>
+      <c r="V141" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -15127,13 +15127,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15228,17 +15228,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -15329,17 +15329,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -15374,7 +15374,7 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -15430,13 +15430,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15531,17 +15531,17 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M146" s="8" t="n">
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -15838,13 +15838,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15939,13 +15939,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16040,13 +16040,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -16141,13 +16141,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -16242,13 +16242,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16343,13 +16343,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16448,13 +16448,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>0</v>
       </c>
       <c r="Q156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R156" s="9" t="n">
         <v>0</v>
@@ -16594,7 +16594,7 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -16654,13 +16654,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>0</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -16856,13 +16856,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>0</v>
       </c>
       <c r="V160" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W160" s="9" t="n">
         <v>0</v>
@@ -17062,13 +17062,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17264,13 +17264,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17365,13 +17365,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17466,13 +17466,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>0</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
@@ -17666,13 +17666,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17771,13 +17771,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17872,13 +17872,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17973,13 +17973,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -18078,17 +18078,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L171" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M171" s="8" t="n">
@@ -18183,13 +18183,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -18284,13 +18284,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -18385,13 +18385,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18591,13 +18591,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -18629,8 +18629,8 @@
       <c r="S176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T176" s="9" t="n">
-        <v>0</v>
+      <c r="T176" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U176" s="9" t="n">
         <v>0</v>
@@ -18696,13 +18696,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>0</v>
       </c>
       <c r="Q178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R178" s="9" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>0</v>
       </c>
       <c r="V178" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
@@ -18898,13 +18898,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -18999,13 +18999,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -19100,13 +19100,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
@@ -19205,13 +19205,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -19407,13 +19407,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
@@ -19512,13 +19512,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>0</v>
       </c>
       <c r="V185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W185" s="9" t="n">
         <v>0</v>
@@ -19617,13 +19617,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -19718,13 +19718,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
@@ -19819,13 +19819,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L188" s="7" t="inlineStr">
         <is>
@@ -19920,17 +19920,17 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L189" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L189" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M189" s="8" t="n">
@@ -20021,13 +20021,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -20122,17 +20122,17 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L191" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L191" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M191" s="8" t="n">
@@ -20227,13 +20227,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>0</v>
       </c>
       <c r="V193" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W193" s="9" t="n">
         <v>0</v>
@@ -20429,13 +20429,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -20530,13 +20530,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
@@ -20635,13 +20635,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -20736,13 +20736,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>10</v>
@@ -20837,13 +20837,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -20866,8 +20866,8 @@
       <c r="P198" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q198" s="9" t="n">
-        <v>1</v>
+      <c r="Q198" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R198" s="9" t="n">
         <v>0</v>
@@ -20882,7 +20882,7 @@
         <v>0</v>
       </c>
       <c r="V198" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W198" s="9" t="n">
         <v>0</v>
@@ -20942,13 +20942,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -21043,13 +21043,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L200" s="7" t="inlineStr">
         <is>
@@ -21148,13 +21148,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21253,13 +21253,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>10</v>
@@ -21459,13 +21459,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
@@ -21503,8 +21503,8 @@
       <c r="U204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V204" s="9" t="n">
-        <v>3</v>
+      <c r="V204" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W204" s="9" t="n">
         <v>0</v>
@@ -21618,7 +21618,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -21633,7 +21633,7 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -21765,7 +21765,7 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21798,7 +21798,7 @@
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21816,7 +21816,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21864,7 +21864,7 @@
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -21882,7 +21882,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -21930,7 +21930,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -21948,7 +21948,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -21963,7 +21963,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -22029,7 +22029,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -22062,7 +22062,7 @@
         <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -22146,7 +22146,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -22311,7 +22311,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -22326,7 +22326,7 @@
         <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -22344,7 +22344,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -22359,7 +22359,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -22458,7 +22458,7 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -22509,7 +22509,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22542,7 +22542,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22575,7 +22575,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -22590,7 +22590,7 @@
         <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -22623,7 +22623,7 @@
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -22788,7 +22788,7 @@
         <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -22806,7 +22806,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -22887,7 +22887,7 @@
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -22905,7 +22905,7 @@
         <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -22938,7 +22938,7 @@
         <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
@@ -905,8 +905,8 @@
       <c r="W2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X2" s="9" t="n">
-        <v>0</v>
+      <c r="X2" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y2" s="9" t="n">
         <v>0</v>
@@ -1006,8 +1006,8 @@
       <c r="W3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X3" s="9" t="n">
-        <v>0</v>
+      <c r="X3" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y3" s="9" t="n">
         <v>0</v>
@@ -1107,8 +1107,8 @@
       <c r="W4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X4" s="9" t="n">
-        <v>0</v>
+      <c r="X4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y4" s="9" t="n">
         <v>0</v>
@@ -1208,8 +1208,8 @@
       <c r="W5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="9" t="n">
-        <v>0</v>
+      <c r="X5" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1309,8 +1309,8 @@
       <c r="W6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="9" t="n">
-        <v>0</v>
+      <c r="X6" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>0</v>
@@ -1414,8 +1414,8 @@
       <c r="W7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X7" s="9" t="n">
-        <v>0</v>
+      <c r="X7" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>0</v>
@@ -1519,8 +1519,8 @@
       <c r="W8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="9" t="n">
-        <v>0</v>
+      <c r="X8" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>0</v>
@@ -1620,8 +1620,8 @@
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>0</v>
+      <c r="X9" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
@@ -1725,8 +1725,8 @@
       <c r="W10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>0</v>
+      <c r="X10" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -1826,8 +1826,8 @@
       <c r="W11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X11" s="9" t="n">
-        <v>0</v>
+      <c r="X11" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>0</v>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
@@ -2028,8 +2028,8 @@
       <c r="W13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X13" s="9" t="n">
-        <v>0</v>
+      <c r="X13" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>0</v>
@@ -2129,8 +2129,8 @@
       <c r="W14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X14" s="9" t="n">
-        <v>0</v>
+      <c r="X14" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
@@ -2230,8 +2230,8 @@
       <c r="W15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X15" s="9" t="n">
-        <v>0</v>
+      <c r="X15" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2331,8 +2331,8 @@
       <c r="W16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X16" s="9" t="n">
-        <v>0</v>
+      <c r="X16" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
@@ -2432,8 +2432,8 @@
       <c r="W17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>0</v>
+      <c r="X17" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="10" t="n">
         <v>1</v>
@@ -2533,8 +2533,8 @@
       <c r="W18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X18" s="9" t="n">
-        <v>0</v>
+      <c r="X18" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
@@ -2634,8 +2634,8 @@
       <c r="W19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X19" s="9" t="n">
-        <v>0</v>
+      <c r="X19" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y20" s="9" t="n">
         <v>0</v>
@@ -2836,8 +2836,8 @@
       <c r="W21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X21" s="9" t="n">
-        <v>0</v>
+      <c r="X21" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X22" s="9" t="n">
-        <v>0</v>
+      <c r="X22" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
@@ -3143,8 +3143,8 @@
       <c r="W24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X24" s="9" t="n">
-        <v>0</v>
+      <c r="X24" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y24" s="9" t="n">
         <v>0</v>
@@ -3244,8 +3244,8 @@
       <c r="W25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X25" s="9" t="n">
-        <v>0</v>
+      <c r="X25" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
@@ -3349,8 +3349,8 @@
       <c r="W26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X26" s="9" t="n">
-        <v>0</v>
+      <c r="X26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y26" s="9" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3400,13 +3400,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3444,14 +3444,14 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>3</v>
+      <c r="V27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X27" s="9" t="n">
-        <v>0</v>
+      <c r="X27" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
@@ -3551,8 +3551,8 @@
       <c r="W28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X28" s="9" t="n">
-        <v>0</v>
+      <c r="X28" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y28" s="9" t="n">
         <v>0</v>
@@ -3652,8 +3652,8 @@
       <c r="W29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X29" s="9" t="n">
-        <v>0</v>
+      <c r="X29" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y29" s="9" t="n">
         <v>0</v>
@@ -3753,8 +3753,8 @@
       <c r="W30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>0</v>
+      <c r="X30" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3839,8 +3839,8 @@
       <c r="R31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="9" t="n">
-        <v>1</v>
+      <c r="S31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T31" s="9" t="n">
         <v>0</v>
@@ -3854,8 +3854,8 @@
       <c r="W31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X31" s="9" t="n">
-        <v>0</v>
+      <c r="X31" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -3955,8 +3955,8 @@
       <c r="W32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="9" t="n">
-        <v>0</v>
+      <c r="X32" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
@@ -4060,8 +4060,8 @@
       <c r="W33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X33" s="9" t="n">
-        <v>0</v>
+      <c r="X33" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
@@ -4161,8 +4161,8 @@
       <c r="W34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X34" s="9" t="n">
-        <v>0</v>
+      <c r="X34" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y34" s="9" t="n">
         <v>0</v>
@@ -4266,8 +4266,8 @@
       <c r="W35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X35" s="9" t="n">
-        <v>0</v>
+      <c r="X35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y35" s="9" t="n">
         <v>0</v>
@@ -4367,8 +4367,8 @@
       <c r="W36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X36" s="9" t="n">
-        <v>0</v>
+      <c r="X36" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y36" s="9" t="n">
         <v>0</v>
@@ -4468,8 +4468,8 @@
       <c r="W37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X37" s="9" t="n">
-        <v>0</v>
+      <c r="X37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y37" s="9" t="n">
         <v>0</v>
@@ -4670,8 +4670,8 @@
       <c r="W39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X39" s="9" t="n">
-        <v>0</v>
+      <c r="X39" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y39" s="9" t="n">
         <v>0</v>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4766,13 +4766,13 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X40" s="9" t="n">
-        <v>0</v>
+      <c r="X40" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y40" s="9" t="n">
         <v>0</v>
@@ -4872,8 +4872,8 @@
       <c r="W41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X41" s="9" t="n">
-        <v>0</v>
+      <c r="X41" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y41" s="9" t="n">
         <v>0</v>
@@ -4973,8 +4973,8 @@
       <c r="W42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X42" s="9" t="n">
-        <v>0</v>
+      <c r="X42" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y42" s="9" t="n">
         <v>0</v>
@@ -5078,8 +5078,8 @@
       <c r="W43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X43" s="9" t="n">
-        <v>0</v>
+      <c r="X43" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y43" s="9" t="n">
         <v>0</v>
@@ -5179,8 +5179,8 @@
       <c r="W44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X44" s="9" t="n">
-        <v>0</v>
+      <c r="X44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y44" s="9" t="n">
         <v>0</v>
@@ -5280,8 +5280,8 @@
       <c r="W45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X45" s="9" t="n">
-        <v>0</v>
+      <c r="X45" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y45" s="9" t="n">
         <v>0</v>
@@ -5385,8 +5385,8 @@
       <c r="W46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X46" s="9" t="n">
-        <v>0</v>
+      <c r="X46" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
@@ -5440,13 +5440,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5485,13 +5485,13 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X47" s="9" t="n">
-        <v>0</v>
+      <c r="X47" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y47" s="9" t="n">
         <v>0</v>
@@ -5595,8 +5595,8 @@
       <c r="W48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X48" s="9" t="n">
-        <v>0</v>
+      <c r="X48" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y48" s="9" t="n">
         <v>0</v>
@@ -5700,8 +5700,8 @@
       <c r="W49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X49" s="9" t="n">
-        <v>0</v>
+      <c r="X49" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y49" s="9" t="n">
         <v>0</v>
@@ -5801,8 +5801,8 @@
       <c r="W50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X50" s="9" t="n">
-        <v>0</v>
+      <c r="X50" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
@@ -5902,8 +5902,8 @@
       <c r="W51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X51" s="9" t="n">
-        <v>0</v>
+      <c r="X51" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
@@ -5953,13 +5953,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -5998,13 +5998,13 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X52" s="9" t="n">
-        <v>0</v>
+      <c r="X52" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y52" s="9" t="n">
         <v>0</v>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6096,8 +6096,8 @@
       <c r="S53" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
+      <c r="T53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U53" s="9" t="n">
         <v>0</v>
@@ -6108,8 +6108,8 @@
       <c r="W53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X53" s="9" t="n">
-        <v>0</v>
+      <c r="X53" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y53" s="9" t="n">
         <v>0</v>
@@ -6209,8 +6209,8 @@
       <c r="W54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X54" s="9" t="n">
-        <v>0</v>
+      <c r="X54" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
@@ -6314,8 +6314,8 @@
       <c r="W55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X55" s="9" t="n">
-        <v>0</v>
+      <c r="X55" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y55" s="9" t="n">
         <v>0</v>
@@ -6415,8 +6415,8 @@
       <c r="W56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X56" s="9" t="n">
-        <v>0</v>
+      <c r="X56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -6516,8 +6516,8 @@
       <c r="W57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X57" s="9" t="n">
-        <v>0</v>
+      <c r="X57" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6621,8 +6621,8 @@
       <c r="W58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X58" s="9" t="n">
-        <v>0</v>
+      <c r="X58" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
@@ -6726,8 +6726,8 @@
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X59" s="9" t="n">
-        <v>0</v>
+      <c r="X59" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="X60" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -6928,8 +6928,8 @@
       <c r="W61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X61" s="9" t="n">
-        <v>0</v>
+      <c r="X61" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y61" s="9" t="n">
         <v>0</v>
@@ -7029,8 +7029,8 @@
       <c r="W62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X62" s="9" t="n">
-        <v>0</v>
+      <c r="X62" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
@@ -7134,8 +7134,8 @@
       <c r="W63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X63" s="9" t="n">
-        <v>0</v>
+      <c r="X63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y63" s="9" t="n">
         <v>0</v>
@@ -7235,8 +7235,8 @@
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X64" s="9" t="n">
-        <v>0</v>
+      <c r="X64" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
@@ -7313,7 +7313,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>1</v>
@@ -7328,7 +7328,7 @@
         <v>1</v>
       </c>
       <c r="U65" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V65" s="10" t="n">
         <v>4</v>
@@ -7336,8 +7336,8 @@
       <c r="W65" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="X65" s="9" t="n">
-        <v>0</v>
+      <c r="X65" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
@@ -7441,8 +7441,8 @@
       <c r="W66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X66" s="9" t="n">
-        <v>0</v>
+      <c r="X66" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7542,8 +7542,8 @@
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X67" s="9" t="n">
-        <v>0</v>
+      <c r="X67" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7643,8 +7643,8 @@
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="9" t="n">
-        <v>0</v>
+      <c r="X68" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
@@ -7744,8 +7744,8 @@
       <c r="W69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X69" s="9" t="n">
-        <v>0</v>
+      <c r="X69" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
@@ -7846,7 +7846,7 @@
         <v>0</v>
       </c>
       <c r="X70" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7946,8 +7946,8 @@
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X71" s="9" t="n">
-        <v>0</v>
+      <c r="X71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="10" t="n">
         <v>2</v>
@@ -8047,8 +8047,8 @@
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="9" t="n">
-        <v>0</v>
+      <c r="X72" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
@@ -8152,8 +8152,8 @@
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X73" s="9" t="n">
-        <v>0</v>
+      <c r="X73" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
@@ -8253,8 +8253,8 @@
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X74" s="9" t="n">
-        <v>0</v>
+      <c r="X74" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
@@ -8358,8 +8358,8 @@
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X75" s="9" t="n">
-        <v>0</v>
+      <c r="X75" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8413,13 +8413,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8463,8 +8463,8 @@
       <c r="W76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X76" s="9" t="n">
-        <v>0</v>
+      <c r="X76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8564,8 +8564,8 @@
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X77" s="9" t="n">
-        <v>0</v>
+      <c r="X77" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8669,8 +8669,8 @@
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X78" s="9" t="n">
-        <v>0</v>
+      <c r="X78" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8720,13 +8720,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8770,8 +8770,8 @@
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X79" s="9" t="n">
-        <v>0</v>
+      <c r="X79" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8871,8 +8871,8 @@
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>0</v>
+      <c r="X80" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -8976,8 +8976,8 @@
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X81" s="9" t="n">
-        <v>0</v>
+      <c r="X81" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -9077,8 +9077,8 @@
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="9" t="n">
-        <v>0</v>
+      <c r="X82" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
@@ -9178,8 +9178,8 @@
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="9" t="n">
-        <v>0</v>
+      <c r="X83" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -9229,13 +9229,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9279,8 +9279,8 @@
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="9" t="n">
-        <v>0</v>
+      <c r="X84" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -9384,8 +9384,8 @@
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="9" t="n">
-        <v>0</v>
+      <c r="X85" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
@@ -9490,7 +9490,7 @@
         <v>0</v>
       </c>
       <c r="X86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
@@ -9590,8 +9590,8 @@
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="9" t="n">
-        <v>0</v>
+      <c r="X87" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9691,8 +9691,8 @@
       <c r="W88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X88" s="9" t="n">
-        <v>0</v>
+      <c r="X88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9792,8 +9792,8 @@
       <c r="W89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X89" s="9" t="n">
-        <v>0</v>
+      <c r="X89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9893,8 +9893,8 @@
       <c r="W90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X90" s="9" t="n">
-        <v>0</v>
+      <c r="X90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -9995,7 +9995,7 @@
         <v>0</v>
       </c>
       <c r="X91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -10095,8 +10095,8 @@
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="9" t="n">
-        <v>0</v>
+      <c r="X92" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -10197,7 +10197,7 @@
         <v>0</v>
       </c>
       <c r="X93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -10297,8 +10297,8 @@
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X94" s="9" t="n">
-        <v>0</v>
+      <c r="X94" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -10399,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="X95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -10504,7 +10504,7 @@
         <v>0</v>
       </c>
       <c r="X96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -10604,8 +10604,8 @@
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="9" t="n">
-        <v>0</v>
+      <c r="X97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
@@ -10705,8 +10705,8 @@
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="9" t="n">
-        <v>0</v>
+      <c r="X98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10806,8 +10806,8 @@
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X99" s="9" t="n">
-        <v>0</v>
+      <c r="X99" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10907,8 +10907,8 @@
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="9" t="n">
-        <v>0</v>
+      <c r="X100" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -10958,13 +10958,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11008,8 +11008,8 @@
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="9" t="n">
-        <v>0</v>
+      <c r="X101" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -11113,8 +11113,8 @@
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="9" t="n">
-        <v>0</v>
+      <c r="X102" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11214,8 +11214,8 @@
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="9" t="n">
-        <v>0</v>
+      <c r="X103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -11315,8 +11315,8 @@
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="9" t="n">
-        <v>0</v>
+      <c r="X104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -11416,8 +11416,8 @@
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="9" t="n">
-        <v>0</v>
+      <c r="X105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -11521,8 +11521,8 @@
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>0</v>
+      <c r="X106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11622,8 +11622,8 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="9" t="n">
-        <v>0</v>
+      <c r="X107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11723,8 +11723,8 @@
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="9" t="n">
-        <v>0</v>
+      <c r="X108" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11829,7 +11829,7 @@
         <v>0</v>
       </c>
       <c r="X109" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11933,8 +11933,8 @@
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="9" t="n">
-        <v>0</v>
+      <c r="X110" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -12035,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="X111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -12135,8 +12135,8 @@
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X112" s="9" t="n">
-        <v>0</v>
+      <c r="X112" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -12236,8 +12236,8 @@
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="9" t="n">
-        <v>0</v>
+      <c r="X113" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12438,8 +12438,8 @@
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X115" s="9" t="n">
-        <v>0</v>
+      <c r="X115" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12540,7 +12540,7 @@
         <v>0</v>
       </c>
       <c r="X116" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -12640,8 +12640,8 @@
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X117" s="9" t="n">
-        <v>0</v>
+      <c r="X117" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12691,13 +12691,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12736,13 +12736,13 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="9" t="n">
-        <v>0</v>
+      <c r="X118" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12846,8 +12846,8 @@
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="9" t="n">
-        <v>0</v>
+      <c r="X119" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12947,8 +12947,8 @@
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="9" t="n">
-        <v>0</v>
+      <c r="X120" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="X121" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -13149,8 +13149,8 @@
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="9" t="n">
-        <v>0</v>
+      <c r="X122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -13250,8 +13250,8 @@
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="9" t="n">
-        <v>0</v>
+      <c r="X123" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -13351,8 +13351,8 @@
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="9" t="n">
-        <v>0</v>
+      <c r="X124" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -13453,7 +13453,7 @@
         <v>0</v>
       </c>
       <c r="X125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13553,8 +13553,8 @@
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="9" t="n">
-        <v>0</v>
+      <c r="X126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13654,8 +13654,8 @@
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X127" s="9" t="n">
-        <v>0</v>
+      <c r="X127" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13756,7 +13756,7 @@
         <v>0</v>
       </c>
       <c r="X128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13851,13 +13851,13 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="9" t="n">
-        <v>0</v>
+      <c r="X129" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13958,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="X130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -14058,8 +14058,8 @@
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="9" t="n">
-        <v>0</v>
+      <c r="X131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -15737,13 +15737,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
@@ -15764,10 +15764,10 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -17652,7 +17652,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17704,8 +17704,8 @@
       <c r="S167" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T167" s="9" t="n">
-        <v>0</v>
+      <c r="T167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U167" s="9" t="n">
         <v>0</v>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18521,14 +18521,14 @@
       <c r="R175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S175" s="9" t="n">
-        <v>1</v>
+      <c r="S175" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T175" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U175" s="9" t="n">
-        <v>0</v>
+      <c r="U175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V175" s="9" t="n">
         <v>3</v>
@@ -19512,13 +19512,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>0</v>
       </c>
       <c r="V185" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W185" s="9" t="n">
         <v>0</v>
@@ -20122,13 +20122,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
@@ -20328,17 +20328,17 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M193" s="8" t="n">
@@ -20355,7 +20355,7 @@
         </is>
       </c>
       <c r="P193" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q193" s="9" t="n">
         <v>1</v>
@@ -20373,7 +20373,7 @@
         <v>0</v>
       </c>
       <c r="V193" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W193" s="9" t="n">
         <v>0</v>
@@ -21043,13 +21043,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L200" s="7" t="inlineStr">
         <is>
@@ -21148,13 +21148,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>0</v>
       </c>
       <c r="V201" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W201" s="9" t="n">
         <v>0</v>
@@ -21783,7 +21783,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -21816,7 +21816,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21981,7 +21981,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -22740,7 +22740,7 @@
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -22806,7 +22806,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -22920,7 +22920,7 @@
         <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">

--- a/docs/d/76/inyear.xlsx
+++ b/docs/d/76/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1402,8 +1402,8 @@
       <c r="S7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="9" t="n">
-        <v>0</v>
+      <c r="T7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U7" s="9" t="n">
         <v>0</v>
@@ -3804,13 +3804,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" s="9" t="n">
         <v>0</v>
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8244,8 +8244,8 @@
       <c r="T74" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U74" s="9" t="n">
-        <v>0</v>
+      <c r="U74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V74" s="9" t="n">
         <v>1</v>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8451,8 +8451,8 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>2</v>
       </c>
       <c r="Q79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8964,8 +8964,8 @@
       <c r="S81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T81" s="9" t="n">
-        <v>0</v>
+      <c r="T81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U81" s="9" t="n">
         <v>0</v>
@@ -9027,13 +9027,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9256,13 +9256,13 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q84" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" s="9" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9843,13 +9843,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9887,8 +9887,8 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>3</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -11471,13 +11471,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S108" s="9" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11912,8 +11912,8 @@
       <c r="P110" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q110" s="9" t="n">
-        <v>1</v>
+      <c r="Q110" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12619,8 +12619,8 @@
       <c r="P117" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q117" s="9" t="n">
-        <v>1</v>
+      <c r="Q117" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -12823,7 +12823,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -13301,13 +13301,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -14159,8 +14159,8 @@
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X132" s="9" t="n">
-        <v>0</v>
+      <c r="X132" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -14260,8 +14260,8 @@
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X133" s="9" t="n">
-        <v>0</v>
+      <c r="X133" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -14361,8 +14361,8 @@
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X134" s="9" t="n">
-        <v>0</v>
+      <c r="X134" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -14462,8 +14462,8 @@
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X135" s="9" t="n">
-        <v>0</v>
+      <c r="X135" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14564,7 +14564,7 @@
         <v>0</v>
       </c>
       <c r="X136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
         <v>0</v>
       </c>
       <c r="X137" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14701,7 +14701,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14753,8 +14753,8 @@
       <c r="S138" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T138" s="9" t="n">
-        <v>0</v>
+      <c r="T138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U138" s="9" t="n">
         <v>0</v>
@@ -14765,8 +14765,8 @@
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X138" s="9" t="n">
-        <v>0</v>
+      <c r="X138" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
@@ -14871,7 +14871,7 @@
         <v>0</v>
       </c>
       <c r="X139" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
@@ -14972,7 +14972,7 @@
         <v>0</v>
       </c>
       <c r="X140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
@@ -15073,7 +15073,7 @@
         <v>0</v>
       </c>
       <c r="X141" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -15279,7 +15279,7 @@
         <v>2</v>
       </c>
       <c r="X143" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -15379,8 +15379,8 @@
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X144" s="9" t="n">
-        <v>0</v>
+      <c r="X144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -15480,8 +15480,8 @@
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X145" s="9" t="n">
-        <v>0</v>
+      <c r="X145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
@@ -15581,8 +15581,8 @@
       <c r="W146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X146" s="9" t="n">
-        <v>0</v>
+      <c r="X146" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
@@ -15686,8 +15686,8 @@
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X147" s="9" t="n">
-        <v>0</v>
+      <c r="X147" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
@@ -15888,8 +15888,8 @@
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X149" s="9" t="n">
-        <v>0</v>
+      <c r="X149" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
@@ -16091,7 +16091,7 @@
         <v>0</v>
       </c>
       <c r="X151" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -16192,7 +16192,7 @@
         <v>0</v>
       </c>
       <c r="X152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
@@ -16292,8 +16292,8 @@
       <c r="W153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X153" s="9" t="n">
-        <v>0</v>
+      <c r="X153" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
@@ -16393,8 +16393,8 @@
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X154" s="9" t="n">
-        <v>0</v>
+      <c r="X154" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
@@ -16498,8 +16498,8 @@
       <c r="W155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X155" s="9" t="n">
-        <v>0</v>
+      <c r="X155" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
@@ -16599,8 +16599,8 @@
       <c r="W156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X156" s="9" t="n">
-        <v>0</v>
+      <c r="X156" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
@@ -16654,13 +16654,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>0</v>
       </c>
       <c r="X157" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
@@ -16805,8 +16805,8 @@
       <c r="W158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X158" s="9" t="n">
-        <v>0</v>
+      <c r="X158" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y158" s="9" t="n">
         <v>0</v>
@@ -16906,8 +16906,8 @@
       <c r="W159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X159" s="9" t="n">
-        <v>0</v>
+      <c r="X159" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y159" s="9" t="n">
         <v>0</v>
@@ -17011,8 +17011,8 @@
       <c r="W160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X160" s="9" t="n">
-        <v>0</v>
+      <c r="X160" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y160" s="9" t="n">
         <v>0</v>
@@ -17112,8 +17112,8 @@
       <c r="W161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X161" s="9" t="n">
-        <v>0</v>
+      <c r="X161" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y161" s="9" t="n">
         <v>0</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="X162" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
@@ -17314,8 +17314,8 @@
       <c r="W163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X163" s="9" t="n">
-        <v>0</v>
+      <c r="X163" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y163" s="9" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>0</v>
       </c>
       <c r="X164" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y164" s="9" t="n">
         <v>0</v>
@@ -17516,8 +17516,8 @@
       <c r="W165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X165" s="9" t="n">
-        <v>0</v>
+      <c r="X165" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
@@ -17615,8 +17615,8 @@
       <c r="W166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X166" s="9" t="n">
-        <v>0</v>
+      <c r="X166" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y166" s="9" t="n">
         <v>0</v>
@@ -17666,13 +17666,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17714,10 +17714,10 @@
         <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X167" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
@@ -17821,8 +17821,8 @@
       <c r="W168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X168" s="9" t="n">
-        <v>0</v>
+      <c r="X168" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
@@ -17922,8 +17922,8 @@
       <c r="W169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X169" s="9" t="n">
-        <v>0</v>
+      <c r="X169" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y169" s="9" t="n">
         <v>0</v>
@@ -18023,8 +18023,8 @@
       <c r="W170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X170" s="9" t="n">
-        <v>0</v>
+      <c r="X170" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
@@ -18128,8 +18128,8 @@
       <c r="W171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X171" s="9" t="n">
-        <v>0</v>
+      <c r="X171" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y171" s="9" t="n">
         <v>0</v>
@@ -18233,8 +18233,8 @@
       <c r="W172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X172" s="9" t="n">
-        <v>0</v>
+      <c r="X172" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y172" s="9" t="n">
         <v>0</v>
@@ -18334,8 +18334,8 @@
       <c r="W173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X173" s="9" t="n">
-        <v>0</v>
+      <c r="X173" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y173" s="9" t="n">
         <v>0</v>
@@ -18435,8 +18435,8 @@
       <c r="W174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X174" s="9" t="n">
-        <v>0</v>
+      <c r="X174" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y174" s="9" t="n">
         <v>0</v>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
@@ -18530,14 +18530,14 @@
       <c r="U175" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V175" s="9" t="n">
-        <v>3</v>
+      <c r="V175" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X175" s="9" t="n">
-        <v>0</v>
+      <c r="X175" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y175" s="9" t="n">
         <v>0</v>
@@ -18641,8 +18641,8 @@
       <c r="W176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X176" s="9" t="n">
-        <v>0</v>
+      <c r="X176" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y176" s="9" t="n">
         <v>0</v>
@@ -18746,8 +18746,8 @@
       <c r="W177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X177" s="9" t="n">
-        <v>0</v>
+      <c r="X177" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y177" s="9" t="n">
         <v>0</v>
@@ -18847,8 +18847,8 @@
       <c r="W178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X178" s="9" t="n">
-        <v>0</v>
+      <c r="X178" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y178" s="9" t="n">
         <v>0</v>
@@ -18898,13 +18898,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -18943,13 +18943,13 @@
         <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X179" s="9" t="n">
-        <v>0</v>
+      <c r="X179" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y179" s="9" t="n">
         <v>0</v>
@@ -19049,8 +19049,8 @@
       <c r="W180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X180" s="9" t="n">
-        <v>0</v>
+      <c r="X180" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y180" s="9" t="n">
         <v>0</v>
@@ -19151,7 +19151,7 @@
         <v>0</v>
       </c>
       <c r="X181" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y181" s="9" t="n">
         <v>0</v>
@@ -19255,8 +19255,8 @@
       <c r="W182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X182" s="9" t="n">
-        <v>0</v>
+      <c r="X182" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y182" s="9" t="n">
         <v>0</v>
@@ -19356,8 +19356,8 @@
       <c r="W183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X183" s="9" t="n">
-        <v>0</v>
+      <c r="X183" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y183" s="9" t="n">
         <v>0</v>
@@ -19457,8 +19457,8 @@
       <c r="W184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X184" s="9" t="n">
-        <v>0</v>
+      <c r="X184" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y184" s="9" t="n">
         <v>0</v>
@@ -19562,8 +19562,8 @@
       <c r="W185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X185" s="9" t="n">
-        <v>0</v>
+      <c r="X185" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y185" s="9" t="n">
         <v>0</v>
@@ -19667,8 +19667,8 @@
       <c r="W186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X186" s="9" t="n">
-        <v>0</v>
+      <c r="X186" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y186" s="9" t="n">
         <v>0</v>
@@ -19869,8 +19869,8 @@
       <c r="W188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X188" s="9" t="n">
-        <v>0</v>
+      <c r="X188" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y188" s="9" t="n">
         <v>0</v>
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -19949,8 +19949,8 @@
       <c r="P189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" s="9" t="n">
-        <v>1</v>
+      <c r="Q189" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R189" s="9" t="n">
         <v>0</v>
@@ -19970,8 +19970,8 @@
       <c r="W189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X189" s="9" t="n">
-        <v>0</v>
+      <c r="X189" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y189" s="9" t="n">
         <v>0</v>
@@ -20071,8 +20071,8 @@
       <c r="W190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X190" s="9" t="n">
-        <v>0</v>
+      <c r="X190" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y190" s="9" t="n">
         <v>0</v>
@@ -20172,8 +20172,8 @@
       <c r="W191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X191" s="9" t="n">
-        <v>0</v>
+      <c r="X191" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y191" s="9" t="n">
         <v>0</v>
@@ -20278,7 +20278,7 @@
         <v>0</v>
       </c>
       <c r="X192" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y192" s="9" t="n">
         <v>0</v>
@@ -20379,7 +20379,7 @@
         <v>0</v>
       </c>
       <c r="X193" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y193" s="9" t="n">
         <v>0</v>
@@ -20480,7 +20480,7 @@
         <v>0</v>
       </c>
       <c r="X194" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y194" s="9" t="n">
         <v>0</v>
@@ -20580,8 +20580,8 @@
       <c r="W195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X195" s="9" t="n">
-        <v>0</v>
+      <c r="X195" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y195" s="9" t="n">
         <v>0</v>
@@ -20686,7 +20686,7 @@
         <v>0</v>
       </c>
       <c r="X196" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y196" s="9" t="n">
         <v>0</v>
@@ -20722,7 +20722,7 @@
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>10</v>
@@ -20763,7 +20763,7 @@
         </is>
       </c>
       <c r="P197" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q197" s="9" t="n">
         <v>0</v>
@@ -20774,8 +20774,8 @@
       <c r="S197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T197" s="9" t="n">
-        <v>0</v>
+      <c r="T197" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U197" s="9" t="n">
         <v>0</v>
@@ -20786,8 +20786,8 @@
       <c r="W197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X197" s="9" t="n">
-        <v>0</v>
+      <c r="X197" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y197" s="9" t="n">
         <v>0</v>
@@ -20887,8 +20887,8 @@
       <c r="W198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X198" s="9" t="n">
-        <v>0</v>
+      <c r="X198" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y198" s="9" t="n">
         <v>0</v>
@@ -20993,7 +20993,7 @@
         <v>0</v>
       </c>
       <c r="X199" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y199" s="9" t="n">
         <v>0</v>
@@ -21093,8 +21093,8 @@
       <c r="W200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X200" s="9" t="n">
-        <v>0</v>
+      <c r="X200" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y200" s="9" t="n">
         <v>0</v>
@@ -21148,13 +21148,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21193,13 +21193,13 @@
         <v>0</v>
       </c>
       <c r="V201" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X201" s="9" t="n">
-        <v>0</v>
+      <c r="X201" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y201" s="9" t="n">
         <v>0</v>
@@ -21303,8 +21303,8 @@
       <c r="W202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X202" s="9" t="n">
-        <v>0</v>
+      <c r="X202" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y202" s="9" t="n">
         <v>0</v>
@@ -21358,13 +21358,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         <v>4</v>
       </c>
       <c r="W203" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X203" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X203" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y203" s="9" t="n">
         <v>0</v>
@@ -21509,8 +21509,8 @@
       <c r="W204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X204" s="9" t="n">
-        <v>0</v>
+      <c r="X204" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y204" s="9" t="n">
         <v>0</v>
@@ -21651,7 +21651,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -22113,7 +22113,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -22146,7 +22146,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -22179,7 +22179,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -22245,7 +22245,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -22377,7 +22377,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -22443,13 +22443,13 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -22575,7 +22575,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -22806,13 +22806,13 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -22872,7 +22872,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -22905,7 +22905,7 @@
         <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
